--- a/inst/extdata/Feed_list_complete.xlsx
+++ b/inst/extdata/Feed_list_complete.xlsx
@@ -37321,8 +37321,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006C01FDD7464A2B4D8E8542CC776211B8" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b2b53f7ad873bd6df00e909b1c26b611">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c084600a-df0b-4cbb-a168-433628fef2ad" xmlns:ns3="a0a235af-62e1-400e-b59d-90d0da600a36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="954ccef8d4159d7504b293d32e65d560" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006C01FDD7464A2B4D8E8542CC776211B8" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3687d2090def2950948841c82405c18d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c084600a-df0b-4cbb-a168-433628fef2ad" xmlns:ns3="a0a235af-62e1-400e-b59d-90d0da600a36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bc008a9ff6ffcf508916b0106aa8f805" ns2:_="" ns3:_="">
     <xsd:import namespace="c084600a-df0b-4cbb-a168-433628fef2ad"/>
     <xsd:import namespace="a0a235af-62e1-400e-b59d-90d0da600a36"/>
     <xsd:element name="properties">
@@ -37344,6 +37344,7 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -37416,6 +37417,11 @@
     <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -37552,7 +37558,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69BA6377-EF77-4189-AC5E-10808E9E0145}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53A67447-1069-4D40-B89E-323B27665F73}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
